--- a/sheets/민요/검수/양류가 (채보1).xlsx
+++ b/sheets/민요/검수/양류가 (채보1).xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I24" s="2"/>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|淋</t>
+          <t xml:space="preserve">–|淋</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 淋</t>
         </is>
       </c>
@@ -1767,12 +1767,12 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="9"/>
@@ -2611,7 +2611,7 @@
       <c r="C10" s="9"/>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 淋</t>
         </is>
       </c>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>

--- a/sheets/민요/검수/양류가 (채보1).xlsx
+++ b/sheets/민요/검수/양류가 (채보1).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2315,57 +2356,57 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">양류가</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">흥을</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">제</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">양</t>
         </is>
@@ -2373,69 +2414,69 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아이</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="26"/>
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="9"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="26"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="C5" s="27"/>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">류</t>
         </is>
@@ -2443,42 +2484,42 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">종을</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">멱</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
@@ -2486,73 +2527,73 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">것</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="26"/>
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H7" s="17"/>
-      <c r="I7" s="9"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="26"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2560,42 +2601,42 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">떠</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">후</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">앞</t>
         </is>
@@ -2603,62 +2644,62 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="C10" s="26"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 淋</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="9"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="26"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">썩</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G11" s="27"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢姑</t>
         </is>
       </c>
-      <c r="I11" s="13" t="inlineStr">
+      <c r="I11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -2666,42 +2707,42 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">앉</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">린</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">끄</t>
         </is>
@@ -2709,43 +2750,43 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">꼬</t>
         </is>
@@ -2753,34 +2794,34 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="G14" s="27"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢姑</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>

--- a/sheets/민요/검수/양류가 (채보1).xlsx
+++ b/sheets/민요/검수/양류가 (채보1).xlsx
@@ -2341,20 +2341,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       <c r="H4" s="23"/>
       <c r="I4" s="26"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
       <c r="H7" s="23"/>
       <c r="I7" s="26"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       <c r="H10" s="23"/>
       <c r="I10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -2792,11 +2792,11 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C14" s="27"/>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="27"/>

--- a/sheets/민요/검수/양류가 (채보1).xlsx
+++ b/sheets/민요/검수/양류가 (채보1).xlsx
@@ -1565,12 +1565,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I27" s="2"/>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E7" s="26"/>

--- a/sheets/민요/검수/양류가 (채보1).xlsx
+++ b/sheets/민요/검수/양류가 (채보1).xlsx
@@ -2378,7 +2378,8 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">흥을</t>
+          <t xml:space="preserve">흥
+을</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -2421,7 +2422,8 @@
       </c>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">아이</t>
+          <t xml:space="preserve">아
+이</t>
         </is>
       </c>
       <c r="D4" s="23" t="inlineStr">
@@ -2501,7 +2503,8 @@
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">종을</t>
+          <t xml:space="preserve">종
+을</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">

--- a/sheets/민요/검수/양류가 (채보1).xlsx
+++ b/sheets/민요/검수/양류가 (채보1).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -234,6 +239,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2376,7 +2399,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">흥
 을</t>
@@ -2387,7 +2410,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2397,7 +2420,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">제</t>
         </is>
@@ -2407,7 +2430,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">양</t>
         </is>
@@ -2420,7 +2443,7 @@
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 이</t>
@@ -2431,19 +2454,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="26"/>
+      <c r="E4" s="32"/>
       <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
       <c r="H4" s="23"/>
-      <c r="I4" s="26"/>
+      <c r="I4" s="32"/>
     </row>
     <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
@@ -2452,13 +2475,13 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C5" s="27"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -2468,7 +2491,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -2478,7 +2501,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">류</t>
         </is>
@@ -2491,7 +2514,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -2501,7 +2524,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">종
 을</t>
@@ -2512,7 +2535,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">멱</t>
         </is>
@@ -2522,7 +2545,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
@@ -2535,7 +2558,7 @@
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">것</t>
         </is>
@@ -2545,19 +2568,19 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="E7" s="26"/>
+      <c r="E7" s="32"/>
       <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
       <c r="H7" s="23"/>
-      <c r="I7" s="26"/>
+      <c r="I7" s="32"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -2566,7 +2589,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -2576,7 +2599,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -2586,7 +2609,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -2596,7 +2619,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I8" s="27" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2609,7 +2632,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -2619,7 +2642,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">떠</t>
         </is>
@@ -2629,7 +2652,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">후</t>
         </is>
@@ -2639,7 +2662,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I9" s="24" t="inlineStr">
+      <c r="I9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">앞</t>
         </is>
@@ -2652,14 +2675,14 @@
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="C10" s="26"/>
+      <c r="C10" s="32"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 淋</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
@@ -2669,9 +2692,9 @@
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="23"/>
-      <c r="I10" s="26"/>
+      <c r="I10" s="32"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -2680,13 +2703,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="33"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E11" s="28" t="inlineStr">
+      <c r="E11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">썩</t>
         </is>
@@ -2696,13 +2719,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢姑</t>
         </is>
       </c>
-      <c r="I11" s="28" t="inlineStr">
+      <c r="I11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -2715,7 +2738,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -2725,7 +2748,7 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">앉</t>
         </is>
@@ -2735,7 +2758,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="G12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">린</t>
         </is>
@@ -2745,7 +2768,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">끄</t>
         </is>
@@ -2758,7 +2781,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -2769,7 +2792,7 @@
 汰</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -2779,7 +2802,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G13" s="26" t="inlineStr">
+      <c r="G13" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -2789,7 +2812,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I13" s="26" t="inlineStr">
+      <c r="I13" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">꼬</t>
         </is>
@@ -2802,13 +2825,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="27"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E14" s="28" t="inlineStr">
+      <c r="E14" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -2818,13 +2841,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="33"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢姑</t>
         </is>
       </c>
-      <c r="I14" s="28" t="inlineStr">
+      <c r="I14" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>

--- a/sheets/민요/검수/양류가 (채보1).xlsx
+++ b/sheets/민요/검수/양류가 (채보1).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,16 +212,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
@@ -238,25 +230,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -353,7 +330,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
     </row>
@@ -365,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
     </row>
@@ -401,7 +378,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 22%</t>
+          <t xml:space="preserve">비고 20%</t>
         </is>
       </c>
     </row>
@@ -429,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12정간, 굵은 선 3칸마다. 오른쪽 여백 "양류가 「바른 굿거리」". "- 197 -"은 양식 용지 번호. 4줄 사용(5~8줄 빈칸). 1·3줄과 2·4줄 가락이 유사. 각 율명 줄 오른쪽 가사 칸을 함께 판독해 가사 열에 적음(1줄=양류상에앞은꾀꼬리, 2줄=제비만멱이서후린다, 3줄=에구좋을다떠들썩앉고서, 4줄=…요것이내사랑). 재판독 때 1~4줄 다수 칸을 南→姑로 바로잡음(손글씨 女+古 확인). 4줄 1·2정간 가사는 흘려 써 불확실.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간, 굵은 선 3칸마다 → 3/4·12. 오른쪽 여백 "양류가 「바른 굿거리」". 오른쪽 4줄 사용(5~8줄 빈칸). 이전 판독의 姑 다수가 실제로는 南(十+冂 흘림)이라 바로잡음; 女+古 모양만 姑. 無 위 작은 ˇ 는 無 첫 획으로 봄. 2·4줄 가락 동일, 1·3줄 끝부분 유사. 가사는 각 율명 줄 오른쪽 칸.</t>
         </is>
       </c>
     </row>
@@ -656,12 +633,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -695,12 +672,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -734,12 +711,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -773,17 +750,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞</t>
+          <t xml:space="preserve">앉</t>
         </is>
       </c>
       <c r="J6" s="4"/>
@@ -812,12 +789,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢姑</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢姑</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -827,7 +804,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">氵계열</t>
+          <t xml:space="preserve">氵+女古, 끝 흘림</t>
         </is>
       </c>
       <c r="K7" s="2"/>
@@ -855,22 +832,22 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">끄</t>
+          <t xml:space="preserve">꾀</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">氵계열</t>
+          <t xml:space="preserve">氵+古 흘림, 㴌로 판단</t>
         </is>
       </c>
       <c r="K8" s="2"/>
@@ -898,12 +875,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">–
+汰</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -937,12 +915,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢姑</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢姑</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -952,7 +930,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">氵계열</t>
+          <t xml:space="preserve">氵 획이 女와 겹침</t>
         </is>
       </c>
       <c r="K10" s="2"/>
@@ -1019,12 +997,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無汰</t>
+          <t xml:space="preserve">無|汰</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無汰</t>
+          <t xml:space="preserve">無
+汰</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1097,12 +1076,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1134,22 +1113,27 @@
       <c r="F15" s="2">
         <v>2</v>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑林</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑林</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|林</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+林</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J15" s="4"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 이/어?</t>
+        </is>
+      </c>
       <c r="K15" s="2"/>
     </row>
     <row r="16">
@@ -1214,12 +1198,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1253,12 +1237,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑林</t>
+          <t xml:space="preserve">南|林</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑林</t>
+          <t xml:space="preserve">南
+林</t>
         </is>
       </c>
       <c r="I18" s="2"/>
@@ -1323,12 +1308,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1362,12 +1347,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1401,12 +1386,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I22" s="2"/>
@@ -1510,12 +1496,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1547,22 +1533,26 @@
       <c r="F26" s="2">
         <v>2</v>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종을</t>
-        </is>
-      </c>
-      <c r="J26" s="4"/>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋을</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 좋을? 흘림</t>
+        </is>
+      </c>
       <c r="K26" s="2"/>
     </row>
     <row r="27">
@@ -1581,22 +1571,26 @@
         <v>3</v>
       </c>
       <c r="E27" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F27" s="2">
         <v>2</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I27" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
       <c r="J27" s="4"/>
       <c r="K27" s="2"/>
     </row>
@@ -1616,24 +1610,24 @@
         <v>3</v>
       </c>
       <c r="E28" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F28" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">다</t>
+          <t xml:space="preserve">떠</t>
         </is>
       </c>
       <c r="J28" s="4"/>
@@ -1655,27 +1649,32 @@
         <v>3</v>
       </c>
       <c r="E29" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F29" s="2">
         <v>3</v>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">떠</t>
-        </is>
-      </c>
-      <c r="J29" s="4"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|淋</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+淋</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">들</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">淋 위에 덧쓴 흔적</t>
+        </is>
+      </c>
       <c r="K29" s="2"/>
     </row>
     <row r="30">
@@ -1694,30 +1693,29 @@
         <v>3</v>
       </c>
       <c r="E30" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F30" s="2">
         <v>3</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|淋</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-淋</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">들</t>
+          <t xml:space="preserve">썩</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">氵계열</t>
+          <t xml:space="preserve">덧쓴 흔적</t>
         </is>
       </c>
       <c r="K30" s="2"/>
@@ -1738,31 +1736,27 @@
         <v>3</v>
       </c>
       <c r="E31" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F31" s="2">
-        <v>3</v>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">썩</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵계열</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앉</t>
+        </is>
+      </c>
+      <c r="J31" s="4"/>
       <c r="K31" s="2"/>
     </row>
     <row r="32">
@@ -1781,31 +1775,28 @@
         <v>3</v>
       </c>
       <c r="E32" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F32" s="2">
         <v>4</v>
       </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앉</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵계열</t>
-        </is>
-      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|汰</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+汰</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
+      <c r="J32" s="4"/>
       <c r="K32" s="2"/>
     </row>
     <row r="33">
@@ -1824,32 +1815,27 @@
         <v>3</v>
       </c>
       <c r="E33" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F33" s="2">
         <v>4</v>
       </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|汰</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">고</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵계열</t>
-        </is>
-      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서</t>
+        </is>
+      </c>
+      <c r="J33" s="4"/>
       <c r="K33" s="2"/>
     </row>
     <row r="34">
@@ -1862,37 +1848,33 @@
         </is>
       </c>
       <c r="C34" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F34" s="2">
-        <v>4</v>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵계열</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥</t>
+        </is>
+      </c>
+      <c r="J34" s="4"/>
       <c r="K34" s="2"/>
     </row>
     <row r="35">
@@ -1911,29 +1893,30 @@
         <v>4</v>
       </c>
       <c r="E35" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="2">
         <v>1</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">無|汰</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">無
+汰</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">흥을</t>
+          <t xml:space="preserve">흥</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">흘려 써 불확실</t>
+          <t xml:space="preserve">가사 흥/훙?</t>
         </is>
       </c>
       <c r="K35" s="2"/>
@@ -1954,31 +1937,23 @@
         <v>4</v>
       </c>
       <c r="E36" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="2">
         <v>1</v>
       </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無汰</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無汰</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아이</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흘려 써 불확실</t>
-        </is>
-      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I36" s="2"/>
+      <c r="J36" s="4"/>
       <c r="K36" s="2"/>
     </row>
     <row r="37">
@@ -1997,22 +1972,26 @@
         <v>4</v>
       </c>
       <c r="E37" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I37" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요</t>
+        </is>
+      </c>
       <c r="J37" s="4"/>
       <c r="K37" s="2"/>
     </row>
@@ -2032,24 +2011,25 @@
         <v>4</v>
       </c>
       <c r="E38" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38" s="2">
         <v>2</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南|林</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南
+林</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">요</t>
+          <t xml:space="preserve">것</t>
         </is>
       </c>
       <c r="J38" s="4"/>
@@ -2071,24 +2051,24 @@
         <v>4</v>
       </c>
       <c r="E39" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F39" s="2">
         <v>2</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑林</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑林</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">것</t>
+          <t xml:space="preserve">이</t>
         </is>
       </c>
       <c r="J39" s="4"/>
@@ -2110,24 +2090,24 @@
         <v>4</v>
       </c>
       <c r="E40" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F40" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이</t>
+          <t xml:space="preserve">내</t>
         </is>
       </c>
       <c r="J40" s="4"/>
@@ -2149,26 +2129,23 @@
         <v>4</v>
       </c>
       <c r="E41" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F41" s="2">
         <v>3</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南|林</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">내</t>
-        </is>
-      </c>
+          <t xml:space="preserve">南
+林</t>
+        </is>
+      </c>
+      <c r="I41" s="2"/>
       <c r="J41" s="4"/>
       <c r="K41" s="2"/>
     </row>
@@ -2188,19 +2165,19 @@
         <v>4</v>
       </c>
       <c r="E42" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F42" s="2">
         <v>3</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑林</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑林</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I42" s="2"/>
@@ -2223,22 +2200,26 @@
         <v>4</v>
       </c>
       <c r="E43" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F43" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I43" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
       <c r="J43" s="4"/>
       <c r="K43" s="2"/>
     </row>
@@ -2258,24 +2239,24 @@
         <v>4</v>
       </c>
       <c r="E44" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F44" s="2">
         <v>4</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사</t>
+          <t xml:space="preserve">랑</t>
         </is>
       </c>
       <c r="J44" s="4"/>
@@ -2297,66 +2278,32 @@
         <v>4</v>
       </c>
       <c r="E45" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F45" s="2">
         <v>4</v>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">랑</t>
-        </is>
-      </c>
-      <c r="J45" s="4"/>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I45" s="3"/>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">– 가 살짝 굽음</t>
+        </is>
+      </c>
       <c r="K45" s="2"/>
     </row>
-    <row r="46">
-      <c r="A46" s="2">
-        <v>1</v>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/양류가.png</t>
-        </is>
-      </c>
-      <c r="C46" s="2">
-        <v>4</v>
-      </c>
-      <c r="D46" s="2">
-        <v>4</v>
-      </c>
-      <c r="E46" s="2">
-        <v>12</v>
-      </c>
-      <c r="F46" s="2">
-        <v>4</v>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I46" s="2"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K46"/>
+  <autoFilter ref="A1:K45"/>
 </worksheet>
 </file>
 
@@ -2377,7 +2324,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="52.21" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2392,396 +2339,396 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="52.21" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흥
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">양</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="52.21" customHeight="1">
+      <c r="A4" s="0"/>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+汰</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+汰</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비</t>
+        </is>
+      </c>
+      <c r="H4" s="21"/>
+      <c r="I4" s="25"/>
+    </row>
+    <row r="5" ht="52.21" customHeight="1">
+      <c r="A5" s="0"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="C5" s="26"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">만</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">류</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52.21" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋
 을</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">멱</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52.21" customHeight="1">
+      <c r="A7" s="0"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+林</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">것</t>
+        </is>
+      </c>
+      <c r="D7" s="21"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+林</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="H7" s="21"/>
+      <c r="I7" s="25"/>
+    </row>
+    <row r="8" ht="52.21" customHeight="1">
+      <c r="A8" s="0"/>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="G3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제</t>
-        </is>
-      </c>
-      <c r="H3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">양</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="55.19" customHeight="1">
-      <c r="A4" s="0"/>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無汰</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아
-이</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E4" s="32"/>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無汰</t>
-        </is>
-      </c>
-      <c r="G4" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비</t>
-        </is>
-      </c>
-      <c r="H4" s="23"/>
-      <c r="I4" s="32"/>
-    </row>
-    <row r="5" ht="55.19" customHeight="1">
-      <c r="A5" s="0"/>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">만</t>
-        </is>
-      </c>
-      <c r="H5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I5" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">류</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종
-을</t>
-        </is>
-      </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">멱</t>
-        </is>
-      </c>
-      <c r="H6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
-      <c r="A7" s="0"/>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑林</t>
-        </is>
-      </c>
-      <c r="C7" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">것</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E7" s="32"/>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑林</t>
-        </is>
-      </c>
-      <c r="G7" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="H7" s="23"/>
-      <c r="I7" s="32"/>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
-      <c r="A8" s="0"/>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서</t>
-        </is>
-      </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
+    </row>
+    <row r="9" ht="52.21" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">떠</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G9" s="30" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">후</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앞</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앉</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52.21" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑林</t>
-        </is>
-      </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+林</t>
+        </is>
+      </c>
+      <c r="C10" s="25"/>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 淋</t>
         </is>
       </c>
-      <c r="E10" s="31" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑林</t>
-        </is>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="32"/>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+林</t>
+        </is>
+      </c>
+      <c r="G10" s="25"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="25"/>
+    </row>
+    <row r="11" ht="52.21" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="C11" s="26"/>
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E11" s="34" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">썩</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G11" s="33"/>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢姑</t>
-        </is>
-      </c>
-      <c r="I11" s="34" t="inlineStr">
+      <c r="G11" s="26"/>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="55.19" customHeight="1">
+    <row r="12" ht="52.21" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C12" s="30" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="E12" s="29" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">앉</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G12" s="30" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">린</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">끄</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I12" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꾀</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52.21" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -2792,62 +2739,65 @@
 汰</t>
         </is>
       </c>
-      <c r="E13" s="31" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G13" s="32" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="H13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I13" s="32" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+汰</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">꼬</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="55.19" customHeight="1">
+    <row r="14" ht="52.21" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C14" s="33"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="C14" s="28"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E14" s="34" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G14" s="33"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢姑</t>
-        </is>
-      </c>
-      <c r="I14" s="34" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="G14" s="26"/>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>

--- a/sheets/민요/검수/양류가 (채보1).xlsx
+++ b/sheets/민요/검수/양류가 (채보1).xlsx
@@ -406,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 12정간, 굵은 선 3칸마다 → 3/4·12. 오른쪽 여백 "양류가 「바른 굿거리」". 오른쪽 4줄 사용(5~8줄 빈칸). 이전 판독의 姑 다수가 실제로는 南(十+冂 흘림)이라 바로잡음; 女+古 모양만 姑. 無 위 작은 ˇ 는 無 첫 획으로 봄. 2·4줄 가락 동일, 1·3줄 끝부분 유사. 가사는 각 율명 줄 오른쪽 칸.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간, 굵은 선 3칸마다 → 3/4·12. 오른쪽 여백 "양류가 「바른 굿거리」". 오른쪽 4줄 사용(5~8줄 빈칸). 이전 판독의 姑 다수가 실제로는 南(十+冂 흘림)이라 바로잡음; 女+古 모양만 姑. 無 위 작은 ˇ 는 無 첫 획으로 봄. 2·4줄 가락 동일, 1·3줄 끝부분 유사. 가사는 각 율명 줄 오른쪽 칸. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋 위에 덧쓴 흔적</t>
+          <t xml:space="preserve">淋 위에 덧쓴 흔적; 淋/㴌?</t>
         </is>
       </c>
       <c r="K29" s="2"/>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">덧쓴 흔적</t>
+          <t xml:space="preserve">덧쓴 흔적; 淋/㴌?</t>
         </is>
       </c>
       <c r="K30" s="2"/>

--- a/sheets/민요/검수/양류가 (채보1).xlsx
+++ b/sheets/민요/검수/양류가 (채보1).xlsx
@@ -418,10 +418,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/양류가 (채보1).xlsx
+++ b/sheets/민요/검수/양류가 (채보1).xlsx
@@ -364,17 +364,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -491,7 +491,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -549,6 +549,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2379,312 +2423,312 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:I14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="43.01" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B3" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="9" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B4" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="22"/>
+      <c r="F4" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="H4" s="18"/>
+      <c r="I4" s="22"/>
+    </row>
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B5" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="12" t="s">
+      <c r="C5" s="23"/>
+      <c r="D5" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="12" t="s">
+      <c r="H5" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="23" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="8" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B6" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="13" t="s">
+      <c r="D6" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" s="8" t="s">
+      <c r="H6" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="19" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B7" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="9" t="s">
+      <c r="D7" s="18"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="11"/>
-    </row>
-    <row r="8" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="H7" s="18"/>
+      <c r="I7" s="22"/>
+    </row>
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="12" t="s">
+      <c r="D8" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" s="12" t="s">
+      <c r="H8" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="23" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="8" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B9" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" s="8" t="s">
+      <c r="H9" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="19" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B10" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="9" t="s">
+      <c r="C10" s="22"/>
+      <c r="D10" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="G10" s="22"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="22"/>
+    </row>
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B11" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="9" t="s">
+      <c r="C11" s="23"/>
+      <c r="D11" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="9" t="s">
+      <c r="G11" s="23"/>
+      <c r="H11" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="25" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="8" t="s">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B12" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="8" t="s">
+      <c r="F12" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="24" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="11" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B13" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="11" t="s">
+      <c r="F13" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="22" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="9" t="s">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B14" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="25"/>
+      <c r="D14" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="9" t="s">
+      <c r="G14" s="23"/>
+      <c r="H14" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="25" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2694,7 +2738,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="93"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/양류가 (채보1).xlsx
+++ b/sheets/민요/검수/양류가 (채보1).xlsx
@@ -2429,13 +2429,13 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
   </cols>
   <sheetData>
